--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
@@ -13,17 +13,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="141">
   <si>
     <t>Framework Coverage</t>
   </si>
   <si>
+    <t>OmniOps</t>
+  </si>
+  <si>
+    <t>CONFIDENTIAL</t>
+  </si>
+  <si>
     <t>Organisation</t>
   </si>
   <si>
-    <t>OmniOps</t>
-  </si>
-  <si>
     <t>Generated by</t>
   </si>
   <si>
@@ -33,13 +36,19 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-17 15:43 UTC</t>
+    <t>2026-09-23 10:59 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
   </si>
   <si>
     <t>SUBTREE</t>
+  </si>
+  <si>
+    <t>Document reference</t>
+  </si>
+  <si>
+    <t>1906-20260923105958</t>
   </si>
   <si>
     <t>Standard</t>
@@ -433,7 +442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -447,6 +456,16 @@
       <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF0F7A5A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF646F85"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="FF646F85"/>
       <sz val="9"/>
     </font>
@@ -457,7 +476,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0B1524"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -474,7 +493,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="FF0F7A5A"/>
       </patternFill>
     </fill>
   </fills>
@@ -508,15 +527,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -525,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -865,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -877,36 +898,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -930,758 +969,758 @@
     <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="G3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="G11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="D12" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="G12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="D14" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="D16" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="G16" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="H16" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D17" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="G18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="B19" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="C19" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="D19" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="G19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D20" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F20" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="G21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="D22" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="G23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="D24" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="G24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="B25" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="C25" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="D25" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="D26" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="G26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D27" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="D28" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>24</v>
+      <c r="D29" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1700,20 +1739,20 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>137</v>
+      <c r="B1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
@@ -36,7 +36,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -48,7 +48,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1906-20260923105958</t>
+    <t>B7C7-20260924223634</t>
   </si>
   <si>
     <t>Standard</t>
